--- a/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
+++ b/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_063_CTRL1_5V" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_063_CTRL1_5V" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_063_CTRL1_5V" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="grilla_Video_063_CTRL1_5V" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="eventos_Video_063_CTRL1_5V" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_063_CTRL1_5V" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_063_CTRL1_5V" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_063_CTRL1_5V" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_063_CTRL1_5V" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_063_CTRL1_5V" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,22 +421,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -459,7 +447,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1014</v>
+        <v>0.103</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
@@ -473,7 +461,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1352</v>
+        <v>0.1373</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
@@ -487,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2028</v>
+        <v>0.2059</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
@@ -501,7 +489,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2704</v>
+        <v>0.2746</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
@@ -515,7 +503,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.338</v>
+        <v>0.3432</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -529,7 +517,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4056</v>
+        <v>0.4119</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
@@ -543,7 +531,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>0.507</v>
+        <v>0.5148</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
@@ -557,7 +545,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6761</v>
+        <v>0.6864</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
@@ -577,111 +565,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>k_usado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>k_automatico</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hay_meseta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>meseta_motivo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>meseta_k_rango</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>conteo_reportable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
@@ -694,77 +712,98 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.86988497077122</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="C2" t="n">
         <v>1848</v>
       </c>
       <c r="D2" t="n">
-        <v>61.83485479797979</v>
+        <v>61.84166666666667</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03380327999994229</v>
+        <v>0.03432219000002272</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06522690706141804</v>
+        <v>0.06536558252822677</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>10.0435606060606</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.514049999999997</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>{'n_eventos': 6, 'hay_estimulacion': True, 'estimulados': array([1, 2, 3, 4]), 'espontaneos': array([0]), 'jitter_limitado_por_resolucion': True, 'z': 14.933, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.065, 'periodo_s': 10.04356, 'periodo_err_s': 0.00432, 'frecuencia_Hz': 0.09957, 'frecuencia_err_Hz': 4.3e-05, 'jitter_s': np.float64(0.00966), 'tolerancia_s': 0.067, 'n_estimulados': 4, 'n_ranuras': 4, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 12.019, 'tren_fin_s': 42.149, 'estimulados_dudosos': array([5]), 'n_estimulados_dudosos': 1, 'dudosos':    indice_evento  tiempo_s  ranura  desvio_s
-0              5    51.858       5   -0.3348, 'resumen_grupos':                  grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
-0          estimulados  4  ...               1.5374           0.0619
-1  estimulados_dudosos  1  ...               1.4945           0.0000
-2          espontaneos  1  ...               0.2946           0.0000
-[3 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
+        <v>6</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>meseta de 6 eventos en k=6..8 (2 puntos) con 0 falsos de control; mesetas posteriores: 5 ev en k=10..20</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.513499999999993</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{'n_eventos': 6, 'hay_estimulacion': True, 'estimulados': array([1, 2, 3, 4, 5]), 'espontaneos': array([0]), 'jitter_limitado_por_resolucion': True, 'z': 17.248, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.0157, 'periodo_s': 9.99917, 'periodo_err_s': 0.00304, 'frecuencia_Hz': 0.10001, 'frecuencia_err_Hz': 3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 11.912, 'tren_fin_s': 51.908, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados  5  ...               1.5325           0.0482
+1  espontaneos  1  ...               0.2950           0.0000
+[2 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
 Columns: [tiempo_s, intervalo_s, frecuencia_Hz]
 Index: [], 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       12.0188     12.0188      0.0       True
-1       2       22.0624     22.0624      0.0       True
-2       3       32.1059     32.1059      0.0       True
-3       4       42.1495     42.1495      0.0       True}</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>29.86988497077122</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.28356433964384</v>
-      </c>
-      <c r="N2" t="n">
-        <v>9.720975100680791</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0334785353535354</v>
-      </c>
-      <c r="P2" t="n">
-        <v>18.97462190812883</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.1914436479319913</v>
+0       1       11.9113     11.9117  0.00033       True
+1       2       21.9105     21.9100 -0.00050       True
+2       3       31.9097     31.9100  0.00033       True
+3       4       41.9088     41.9083 -0.00050       True
+4       5       51.9080     51.9083  0.00033       True}</t>
+        </is>
       </c>
       <c r="R2" t="n">
-        <v>11.36736499677406</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="S2" t="n">
-        <v>12.81039372152724</v>
+        <v>0.2836873523097097</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3893244504196559</v>
+        <v>9.704559794101344</v>
       </c>
       <c r="U2" t="n">
-        <v>13.34657698273776</v>
+        <v>0.03333333333333144</v>
+      </c>
+      <c r="V2" t="n">
+        <v>18.981837132304</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1916672991127788</v>
+      </c>
+      <c r="X2" t="n">
+        <v>11.35650029823861</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12.82467274528135</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.3890124534645679</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>13.30758874007001</v>
       </c>
     </row>
   </sheetData>
@@ -778,56 +817,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -840,82 +879,56 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>12.02</v>
+        <v>11.91</v>
       </c>
       <c r="D2" t="n">
-        <v>42.15</v>
+        <v>51.91</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0436</v>
+        <v>9.9992</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5374</v>
+        <v>1.5325</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0619</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>estimulados_dudosos</t>
+          <t>espontaneos</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>51.86</v>
+        <v>0.31</v>
       </c>
       <c r="D3" t="n">
-        <v>51.86</v>
+        <v>0.31</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>1.4945</v>
+        <v>0.295</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>0.2946</v>
-      </c>
-      <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -930,31 +943,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -965,13 +978,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12.0188</v>
+        <v>11.9113</v>
       </c>
       <c r="C2" t="n">
-        <v>12.0188</v>
+        <v>11.9117</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -982,13 +995,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>22.0624</v>
+        <v>21.9105</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0624</v>
+        <v>21.91</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -999,13 +1012,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>32.1059</v>
+        <v>31.9097</v>
       </c>
       <c r="C4" t="n">
-        <v>32.1059</v>
+        <v>31.91</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.00033</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1016,15 +1029,32 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>42.1495</v>
+        <v>41.9088</v>
       </c>
       <c r="C5" t="n">
-        <v>42.1495</v>
+        <v>41.9083</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>51.908</v>
+      </c>
+      <c r="C6" t="n">
+        <v>51.9083</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00033</v>
+      </c>
+      <c r="E6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1043,17 +1073,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
@@ -1064,10 +1094,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3682638888888889</v>
+        <v>0.3083333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2946000000000026</v>
+        <v>0.2949999999999591</v>
       </c>
     </row>
     <row r="3">
@@ -1075,10 +1105,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>12.01879419191919</v>
+        <v>11.91166666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>1.541200000000003</v>
+        <v>1.542700000000025</v>
       </c>
     </row>
     <row r="4">
@@ -1086,7 +1116,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>22.0623547979798</v>
+        <v>21.91</v>
       </c>
       <c r="C4" t="n">
         <v>1.56389999999999</v>
@@ -1097,10 +1127,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>32.1059154040404</v>
+        <v>31.91</v>
       </c>
       <c r="C5" t="n">
-        <v>1.533599999999979</v>
+        <v>1.53249999999997</v>
       </c>
     </row>
     <row r="6">
@@ -1108,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>42.149476010101</v>
+        <v>41.90833333333334</v>
       </c>
       <c r="C6" t="n">
         <v>1.338999999999999</v>
@@ -1119,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>51.85825126262626</v>
+        <v>51.90833333333334</v>
       </c>
       <c r="C7" t="n">
         <v>1.494500000000016</v>

--- a/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
+++ b/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_063_CTRL1_5V" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_063_CTRL1_5V" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_063_CTRL1_5V" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_063_CTRL1_5V" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +703,96 @@
       <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
         </is>
       </c>
     </row>
@@ -804,6 +895,56 @@
       </c>
       <c r="AA2" t="n">
         <v>13.30758874007001</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5288297005004277</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4814-0.5381</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.1000000000000007</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.09916666666666735</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>TTP: 2 fotogramas (&lt; 5); solo cota TTP &lt; 100 ms; RT50: 2 fotogramas (&lt; 5); solo cota RT50 &lt; 99 ms</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1158,4 +1299,550 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3083333333333333</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2949999999999591</v>
+      </c>
+      <c r="F2" t="n">
+        <v>286.2128908467356</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1030701304638053</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2585205551191377</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.04981277821419561</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0421363392377927</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.09833333333333327</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3685664442910827</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.110045889171945</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>359</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.91166666666667</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.542700000000025</v>
+      </c>
+      <c r="F3" t="n">
+        <v>286.2162371232308</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5389980720541068</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>11.8656401956553</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04602647101137158</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.04917360079246791</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.09666666666666934</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>12.01038221076378</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1447420151084859</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>659</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.56389999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>286.2730535234541</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5462966146311988</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21.87281448452912</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.03718551547088467</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1000000000000085</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.04915234822451708</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>22.05457523809524</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1817607535661203</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>959</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.53249999999997</v>
+      </c>
+      <c r="F5" t="n">
+        <v>286.189709875471</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5354839629512896</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>31.87028161530287</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03971838469713163</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1000000000000085</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.05099683387751597</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>32.0474145785877</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.17713296328483</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1259</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41.90833333333334</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.338999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>286.1985945682703</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4678569445876825</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>41.87692986065395</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03140347267939347</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06499999999999773</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.05236529440133353</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>42.03088949605343</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.153959635399481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1549</v>
+      </c>
+      <c r="D7" t="n">
+        <v>51.90833333333334</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.494500000000016</v>
+      </c>
+      <c r="F7" t="n">
+        <v>286.2064913628045</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5221754380495656</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>51.87308189226793</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.03525144106540523</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.05463555486186777</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>52.03772169582119</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.164639803553257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
+++ b/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,83 +459,83 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1373</v>
+        <v>0.1133</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2059</v>
+        <v>0.1246</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2746</v>
+        <v>0.137</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3432</v>
+        <v>0.1507</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4119</v>
+        <v>0.1658</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5148</v>
+        <v>0.1824</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -543,15 +543,225 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6864</v>
+        <v>0.2006</v>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7.074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7.781</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8.558999999999999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.414999999999999</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="C14" t="n">
         <v>5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11.392</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12.532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13.785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15.163</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5204</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18.348</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.6297</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20.182</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.6927</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22.201</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24.421</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.8381999999999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -566,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +1005,61 @@
           <t>cinetica_motivo</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida_pct</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>fotogramas_low_quality</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>eventos_junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>win_s_usado</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>win_s_automatico</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>duracion_evento_max_s</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>ventana_corta</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>conteo_por_ventana</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>conteo_estable_ventana</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>mesetas</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -824,7 +1089,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.431</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -834,12 +1099,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>meseta de 6 eventos en k=6..8 (2 puntos) con 0 falsos de control; mesetas posteriores: 5 ev en k=10..20</t>
+          <t>meseta de 6 eventos en k=5.315..8.559 (x1.61) con 0 falsos de control; OTRAS MESETAS: 5 ev en k=9.415..24.421</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>5.315-8.559</t>
         </is>
       </c>
       <c r="N2" t="b">
@@ -944,6 +1209,43 @@
       <c r="AS2" t="inlineStr">
         <is>
           <t>TTP: 2 fotogramas (&lt; 5); solo cota TTP &lt; 100 ms; RT50: 2 fotogramas (&lt; 5); solo cota RT50 &lt; 99 ms</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.1999999999999886</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
+        </is>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6 ev en k=5.315-8.559; 5 ev en k=9.415-24.421</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,6 +1531,11 @@
           <t>amplitud_px</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1239,6 +1546,9 @@
       </c>
       <c r="C2" t="n">
         <v>0.2949999999999591</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1251,6 +1561,9 @@
       <c r="C3" t="n">
         <v>1.542700000000025</v>
       </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1262,6 +1575,9 @@
       <c r="C4" t="n">
         <v>1.56389999999999</v>
       </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1273,6 +1589,9 @@
       <c r="C5" t="n">
         <v>1.53249999999997</v>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1284,6 +1603,9 @@
       <c r="C6" t="n">
         <v>1.338999999999999</v>
       </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1616,9 @@
       </c>
       <c r="C7" t="n">
         <v>1.494500000000016</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
+++ b/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_063_CTRL1_5V" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_063_CTRL1_5V" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_063_CTRL1_5V" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_063_CTRL1_5V" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_063_CTRL1_5V" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_063_CTRL1_5V" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="estab_Video_063_CTRL1_5V" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen_Video_063_CTRL1_5V" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ritmo_Video_063_CTRL1_5V" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="trenes_Video_063_CTRL1_5V" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="grilla_Video_063_CTRL1_5V" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="eventos_Video_063_CTRL1_5V" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="cinetica_Video_063_CTRL1_5V" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="cin_grupos_Video_063_CTRL1_" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,22 +436,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -448,13 +462,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.103</v>
+        <v>0.0725</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -462,13 +476,13 @@
         <v>3.3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1133</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -476,13 +490,13 @@
         <v>3.63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1246</v>
+        <v>0.0877</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -490,13 +504,13 @@
         <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>0.137</v>
+        <v>0.0965</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -504,13 +518,13 @@
         <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1507</v>
+        <v>0.1061</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -518,13 +532,13 @@
         <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1658</v>
+        <v>0.1168</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -532,13 +546,13 @@
         <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1824</v>
+        <v>0.1284</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -546,13 +560,13 @@
         <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2006</v>
+        <v>0.1413</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -560,13 +574,13 @@
         <v>6.431</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2207</v>
+        <v>0.1554</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -574,13 +588,13 @@
         <v>7.074</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2428</v>
+        <v>0.171</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -588,13 +602,13 @@
         <v>7.781</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2671</v>
+        <v>0.188</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -602,13 +616,13 @@
         <v>8.558999999999999</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2938</v>
+        <v>0.2068</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -616,10 +630,10 @@
         <v>9.414999999999999</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3231</v>
+        <v>0.2275</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -630,10 +644,10 @@
         <v>10.357</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3555</v>
+        <v>0.2503</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -644,10 +658,10 @@
         <v>11.392</v>
       </c>
       <c r="B16" t="n">
-        <v>0.391</v>
+        <v>0.2753</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -658,10 +672,10 @@
         <v>12.532</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4301</v>
+        <v>0.3029</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -672,10 +686,10 @@
         <v>13.785</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4731</v>
+        <v>0.3331</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -686,7 +700,7 @@
         <v>15.163</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5204</v>
+        <v>0.3664</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
@@ -700,7 +714,7 @@
         <v>16.68</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5725</v>
+        <v>0.4031</v>
       </c>
       <c r="C20" t="n">
         <v>5</v>
@@ -714,7 +728,7 @@
         <v>18.348</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6297</v>
+        <v>0.4434</v>
       </c>
       <c r="C21" t="n">
         <v>5</v>
@@ -728,7 +742,7 @@
         <v>20.182</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6927</v>
+        <v>0.4877</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
@@ -742,7 +756,7 @@
         <v>22.201</v>
       </c>
       <c r="B23" t="n">
-        <v>0.762</v>
+        <v>0.5365</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
@@ -756,7 +770,7 @@
         <v>24.421</v>
       </c>
       <c r="B24" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="C24" t="n">
         <v>5</v>
@@ -776,288 +790,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD2"/>
+  <dimension ref="A1:BK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_grupo_principal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>mesetas</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_sup_px</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_inf_px</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>cociente_ruido_bordes</t>
         </is>
       </c>
     </row>
@@ -1080,16 +1129,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03432219000002272</v>
+        <v>0.02416638000000162</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06536558252822677</v>
+        <v>0.04949850326609984</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.431</v>
+        <v>11.392</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -1099,12 +1148,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>meseta de 6 eventos en k=5.315..8.559 (x1.61) con 0 falsos de control; OTRAS MESETAS: 5 ev en k=9.415..24.421</t>
+          <t>meseta de 6 eventos en k=9.415..13.785 (x1.46) con 0 falsos de control; OTRAS MESETAS: 5 ev en k=15.163..24.421</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>5.315-8.559</t>
+          <t>9.415-13.785</t>
         </is>
       </c>
       <c r="N2" t="b">
@@ -1114,139 +1163,169 @@
         <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>1.513499999999993</v>
+        <v>1.589799999999997</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 6, 'hay_estimulacion': True, 'estimulados': array([1, 2, 3, 4, 5]), 'espontaneos': array([0]), 'jitter_limitado_por_resolucion': True, 'z': 17.248, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.0157, 'periodo_s': 9.99917, 'periodo_err_s': 0.00304, 'frecuencia_Hz': 0.10001, 'frecuencia_err_Hz': 3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 11.912, 'tren_fin_s': 51.908, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
-0  estimulados  5  ...               1.5325           0.0482
-1  espontaneos  1  ...               0.2950           0.0000
+          <t>{'n_eventos': 6, 'fuente_tiempo': 'inicio (onset 10 %) en 6 de 6 eventos; pico en el resto', 'modo_busqueda': 'dirigida', 'trenes':    tren           busqueda  ... inicio_s   fin_s
+0     1  dirigida a 0.1 Hz  ...   11.875  51.867
+[1 rows x 17 columns], 'dudosos': Empty DataFrame
+Columns: []
+Index: [], 'sacados_tiempo_amplitud': Empty DataFrame
+Columns: []
+Index: [], 'grupo_por_evento': array(['espontaneos', 'estimulados', 'estimulados', 'estimulados',
+       'estimulados', 'estimulados'], dtype=object), 'tren_por_evento': array([0, 1, 1, 1, 1, 1]), 'estimulados': array([1, 2, 3, 4, 5]), 'estimulados_dudosos': array([], dtype=int64), 'espontaneos': array([0]), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 17.247, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9682, 'periodo_s': 9.99812, 'periodo_err_s': 0.00304, 'frecuencia_Hz': 0.10002, 'frecuencia_err_Hz': 3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 11.875, 'tren_fin_s': 51.867, 'jitter_limitado_por_resolucion': True, 'resumen_grupos':          grupo  n  t_inicio_s  ...  CV_intervalo_pct  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados  5       11.88  ...               0.1               1.5915           0.0541
+1  espontaneos  1        0.26  ...               NaN               0.3625           0.0000
 [2 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
 Columns: [tiempo_s, intervalo_s, frecuencia_Hz]
-Index: [], 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       11.9113     11.9117  0.00033       True
-1       2       21.9105     21.9100 -0.00050       True
-2       3       31.9097     31.9100  0.00033       True
-3       4       41.9088     41.9083 -0.00050       True
-4       5       51.9080     51.9083  0.00033       True}</t>
+Index: [], 'grilla':    tren  ranura  t_esperado_s  t_medido_s  error_s  capturada
+0     1       1       11.8769     11.8755 -0.00141       True
+1     1       2       21.8750     21.8782  0.00319       True
+2     1       3       31.8731     31.8684 -0.00472       True
+3     1       4       41.8713     41.8768  0.00550       True
+4     1       5       51.8694     51.8668 -0.00257       True}</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>30.00000000000171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2836873523097097</v>
+        <v>0.3209169896100662</v>
       </c>
       <c r="T2" t="n">
-        <v>9.704559794101344</v>
+        <v>14.49725055412253</v>
       </c>
       <c r="U2" t="n">
         <v>0.03333333333333144</v>
       </c>
       <c r="V2" t="n">
-        <v>18.981837132304</v>
+        <v>20.20302617693027</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1916672991127788</v>
+        <v>0.1661615960436848</v>
       </c>
       <c r="X2" t="n">
-        <v>11.35650029823861</v>
+        <v>13.00122330561819</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.82467274528135</v>
+        <v>10.46054644395736</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3890124534645679</v>
+        <v>0.3525110956406138</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.30758874007001</v>
-      </c>
-      <c r="AB2" t="n">
+        <v>15.92449711939442</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
         <v>5</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0.5288297005004277</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4814-0.5381</t>
-        </is>
+      <c r="AD2" t="n">
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="n">
+        <v>0.5638313916458232</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.5627-0.5819</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
       </c>
-      <c r="AG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.1000000000000007</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>6</v>
-      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>2</v>
       </c>
-      <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.09916666666666735</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>TTP: 2 fotogramas (&lt; 5); solo cota TTP &lt; 100 ms; RT50: 2 fotogramas (&lt; 5); solo cota RT50 &lt; 99 ms</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>TTP: medible en 0 de 5 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 100 ms; RT50: medible en 0 de 5 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 100 ms</t>
+        </is>
       </c>
       <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
         <v>2</v>
       </c>
-      <c r="AY2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.1999999999999886</v>
-      </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.2333333333333201</v>
+      </c>
+      <c r="BE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
         </is>
       </c>
-      <c r="BC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>6 ev en k=5.315-8.559; 5 ev en k=9.415-24.421</t>
-        </is>
+      <c r="BG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>6 ev en k=9.415-13.785; 5 ev en k=15.163-24.421</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.03513762000002872</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.03217241999984601</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.092165898623632</v>
       </c>
     </row>
   </sheetData>
@@ -1264,52 +1343,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1325,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>11.91</v>
+        <v>11.88</v>
       </c>
       <c r="D2" t="n">
-        <v>51.91</v>
+        <v>51.87</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9992</v>
+        <v>9.996499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5325</v>
+        <v>1.5915</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0482</v>
+        <v>0.0541</v>
       </c>
     </row>
     <row r="3">
@@ -1359,17 +1438,17 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="D3" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.295</v>
+        <v>0.3625</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1386,33 +1465,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ranura</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>t_esperado_s</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>t_medido_s</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>error_s</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>capturada</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>busqueda</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>veredicto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>clasificacion</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>periodo_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>periodo_err_s</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>frecuencia_Hz</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>jitter_ms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p_valor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_tren</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>n_ranuras</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>captura_pct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_dudosos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>n_sacados_tiempo_amplitud</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>inicio_s</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fin_s</t>
         </is>
       </c>
     </row>
@@ -1420,85 +1559,59 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>11.9113</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11.9117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00033</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>21.9105</v>
-      </c>
-      <c r="C3" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>31.9097</v>
-      </c>
-      <c r="C4" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.00033</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>41.9088</v>
-      </c>
-      <c r="C5" t="n">
-        <v>41.9083</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dirigida a 0.1 Hz</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>enganchado a la frecuencia configurada (0.1 Hz)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9.99812</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.00304</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.10002</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>17.247</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>51.908</v>
-      </c>
-      <c r="C6" t="n">
-        <v>51.9083</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.00033</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>51.867</v>
       </c>
     </row>
   </sheetData>
@@ -1512,28 +1625,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>evento</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>junto_a_hueco</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ranura</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>t_esperado_s</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t_medido_s</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>error_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>capturada</t>
         </is>
       </c>
     </row>
@@ -1542,83 +1665,99 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3083333333333333</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2949999999999591</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
+        <v>11.8769</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11.8755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.00141</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>11.91166666666667</v>
-      </c>
       <c r="C3" t="n">
-        <v>1.542700000000025</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
+        <v>21.875</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.8782</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>21.91</v>
-      </c>
       <c r="C4" t="n">
-        <v>1.56389999999999</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
+        <v>31.8731</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31.8684</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.00472</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>31.91</v>
-      </c>
       <c r="C5" t="n">
-        <v>1.53249999999997</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
+        <v>41.8713</v>
+      </c>
+      <c r="D5" t="n">
+        <v>41.8768</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>41.90833333333334</v>
-      </c>
       <c r="C6" t="n">
-        <v>1.338999999999999</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>51.90833333333334</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.494500000000016</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
+        <v>51.8694</v>
+      </c>
+      <c r="D6" t="n">
+        <v>51.8668</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1632,118 +1771,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
         </is>
       </c>
     </row>
@@ -1751,420 +1800,973 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
+      <c r="B2" t="n">
+        <v>0.3083333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.3083333333333333</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.2949999999999591</v>
-      </c>
-      <c r="F2" t="n">
-        <v>286.2128908467356</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.1030701304638053</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.2585205551191377</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.04981277821419561</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.0421363392377927</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.09833333333333327</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.3685664442910827</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.110045889171945</v>
+        <v>0.3624500000000239</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B3" t="n">
+        <v>11.91166666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>359</v>
-      </c>
-      <c r="D3" t="n">
-        <v>11.91166666666667</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.542700000000025</v>
-      </c>
-      <c r="F3" t="n">
-        <v>286.2162371232308</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.5389980720541068</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>11.8656401956553</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.04602647101137158</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.04917360079246791</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.09666666666666934</v>
-      </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>12.01038221076378</v>
-      </c>
-      <c r="U3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.1447420151084859</v>
+        <v>1.644399999999962</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B4" t="n">
+        <v>21.91</v>
       </c>
       <c r="C4" t="n">
-        <v>659</v>
-      </c>
-      <c r="D4" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.56389999999999</v>
-      </c>
-      <c r="F4" t="n">
-        <v>286.2730535234541</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5462966146311988</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>21.87281448452912</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.03718551547088467</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.1000000000000085</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.04915234822451708</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>22.05457523809524</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1817607535661203</v>
+        <v>1.591499999999996</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B5" t="n">
+        <v>31.91</v>
       </c>
       <c r="C5" t="n">
-        <v>959</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.53249999999997</v>
-      </c>
-      <c r="F5" t="n">
-        <v>286.189709875471</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5354839629512896</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>31.87028161530287</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.03971838469713163</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.1000000000000085</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.05099683387751597</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>32.0474145785877</v>
-      </c>
-      <c r="U5" t="n">
-        <v>7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.17713296328483</v>
+        <v>1.642200000000003</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B6" t="n">
+        <v>41.90833333333334</v>
       </c>
       <c r="C6" t="n">
-        <v>1259</v>
-      </c>
-      <c r="D6" t="n">
-        <v>41.90833333333334</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.338999999999999</v>
-      </c>
-      <c r="F6" t="n">
-        <v>286.1985945682703</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.4678569445876825</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>41.87692986065395</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.03140347267939347</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.06499999999999773</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.05236529440133353</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>42.03088949605343</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.153959635399481</v>
+        <v>1.476100000000031</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
+      <c r="B7" t="n">
+        <v>51.90833333333334</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.588099999999997</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3083333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3624500000000239</v>
+      </c>
+      <c r="G2" t="n">
+        <v>282.2280132137913</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1284245301778259</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2560361885790169</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0522971447543164</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.04237293932553299</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.09833333333333327</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3705407346603723</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1145045460813554</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>359</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11.91166666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.644399999999962</v>
+      </c>
+      <c r="G3" t="n">
+        <v>282.2092391233977</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5826882227909406</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11.87549220051491</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03617446615175623</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.04801368061036193</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.09666666666666934</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>12.01312337294851</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1376311724335952</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>659</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.591499999999996</v>
+      </c>
+      <c r="G4" t="n">
+        <v>282.2652345330418</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5638313916458232</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.87821873127871</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.03178126872129283</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.06666666666666998</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05053973302491954</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>22.06191176470589</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1836930334271862</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>959</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.642200000000003</v>
+      </c>
+      <c r="G5" t="n">
+        <v>282.199208913609</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5819293421558588</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.86843231162197</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.04156768837803426</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1000000000000085</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.05105462412115358</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>32.01879704301076</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1503647313887981</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41.90833333333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.476100000000031</v>
+      </c>
+      <c r="G6" t="n">
+        <v>282.2543039692083</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5229681104033976</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.87677143821742</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03156189511591379</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.06499999999999773</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0517839004570817</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>42.02637431693989</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1496028787224688</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>estimulados</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>1549</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>51.90833333333334</v>
       </c>
-      <c r="E7" t="n">
-        <v>1.494500000000016</v>
-      </c>
       <c r="F7" t="n">
-        <v>286.2064913628045</v>
+        <v>1.588099999999997</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5221754380495656</v>
+        <v>282.236726893712</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.5626836795758556</v>
       </c>
       <c r="I7" t="n">
-        <v>51.87308189226793</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
+        <v>51.86682667934094</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.03525144106540523</v>
-      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.04150665399239983</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.1000000000000014</v>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" t="n">
-        <v>0.05463555486186777</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.05077394072985442</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.1000000000000014</v>
       </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>52.03772169582119</v>
+      <c r="T7" t="b">
+        <v>0</v>
       </c>
       <c r="U7" t="n">
+        <v>52.03418753365644</v>
+      </c>
+      <c r="V7" t="n">
         <v>6</v>
       </c>
-      <c r="V7" t="n">
-        <v>0.164639803553257</v>
+      <c r="W7" t="n">
+        <v>0.1673608543155041</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5632575356108394</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5329-0.5774</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.09999999999999981</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.09916666666666735</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TTP: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 100 ms; RT50: medible en 0 de 6 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 99 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5638313916458232</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.5627-0.5819</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TTP: medible en 0 de 5 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 100 ms; RT50: medible en 0 de 5 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 100 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1284245301778259</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.09833333333333327</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TTP: medible en 0 de 1 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota TTP &lt; 100 ms; RT50: medible en 0 de 1 eventos (&lt; la mitad con &gt;= 5 fotogramas); solo cota RT50 &lt; 98 ms</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
+++ b/data/processed_data/Video_063_CTRL1_5V/contracciones.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,22 +424,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -790,321 +778,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>eventos_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1294,37 +1287,40 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
         <v>2</v>
       </c>
-      <c r="BC2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
         <v>0.2333333333333201</v>
       </c>
-      <c r="BE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
         </is>
       </c>
-      <c r="BG2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>6 ev en k=9.415-13.785; 5 ev en k=15.163-24.421</t>
         </is>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>0.03513762000002872</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>0.03217241999984601</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>1.092165898623632</v>
       </c>
     </row>
@@ -1343,52 +1339,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1469,87 +1465,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1629,32 +1625,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1771,28 +1767,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>junto_al_borde</t>
         </is>
       </c>
     </row>
@@ -1808,6 +1809,9 @@
       </c>
       <c r="D2" t="b">
         <v>0</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1823,6 +1827,9 @@
       <c r="D3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1837,6 +1844,9 @@
       <c r="D4" t="b">
         <v>0</v>
       </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1851,6 +1861,9 @@
       <c r="D5" t="b">
         <v>0</v>
       </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1865,6 +1878,9 @@
       <c r="D6" t="b">
         <v>0</v>
       </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1877,6 +1893,9 @@
         <v>1.588099999999997</v>
       </c>
       <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1895,117 +1914,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -2464,112 +2483,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
